--- a/backups/clients.xlsx
+++ b/backups/clients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,53 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>SEO, Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CID02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mark  |  32434334231  |  Mark@facebook.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | | </t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | | </t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>In-process</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CEO</t>
         </is>
       </c>
     </row>
